--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513658_FASEFINALAFFA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513658_FASEFINALAFFA2_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2889</v>
+        <v>3.3593</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0125</v>
+        <v>3.0066</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2764</v>
+        <v>0.3526</v>
       </c>
       <c r="G2" t="n">
-        <v>0.719</v>
+        <v>0.5553</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5921</v>
+        <v>0.8945</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3111</v>
+        <v>-0.3391</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0347</v>
+        <v>2.7223</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3027</v>
+        <v>1.401</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3374</v>
+        <v>1.3213</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3157</v>
+        <v>-2.167</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2895</v>
+        <v>-0.5065</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0262</v>
+        <v>-1.6604</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3632</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1947</v>
+        <v>-3.5053</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5579</v>
+        <v>2.5316</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2068</v>
+        <v>0.1144</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1726</v>
+        <v>0.1265</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0342</v>
+        <v>-0.012</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3.6632</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.6632</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.97</v>
+        <v>3.278</v>
       </c>
       <c r="E3" t="n">
-        <v>2.909</v>
+        <v>1.4424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.061</v>
+        <v>1.8356</v>
       </c>
       <c r="G3" t="n">
-        <v>0.659</v>
+        <v>1.6016</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0771</v>
+        <v>1.8042</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7361</v>
+        <v>-0.2026</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3496</v>
+        <v>2.3884</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4259</v>
+        <v>2.299</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7754</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6906</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6513</v>
+        <v>-0.4947</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0394</v>
+        <v>-0.292</v>
       </c>
       <c r="P3" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1.1684</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-3.1158</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.9474</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0958</v>
+        <v>0.099</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4015</v>
+        <v>0.2224</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3057</v>
+        <v>-0.1235</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3837</v>
+        <v>0.9932</v>
       </c>
       <c r="W3" t="n">
-        <v>4.2737</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.89</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7401</v>
+        <v>3.1926</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0437</v>
+        <v>2.909</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6964</v>
+        <v>0.2837</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6016</v>
+        <v>0.659</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8042</v>
+        <v>-1.0771</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2026</v>
+        <v>1.7361</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3884</v>
+        <v>1.3496</v>
       </c>
       <c r="K4" t="n">
-        <v>2.299</v>
+        <v>-0.4259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.7754</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.6906</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4947</v>
+        <v>-0.6513</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.292</v>
+        <v>-0.0394</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1684</v>
+        <v>-3.1158</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7526</v>
+        <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4389</v>
+        <v>0.3184</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1763</v>
+        <v>0.4015</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2626</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9932</v>
+        <v>3.3837</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.2737</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9932</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5618</v>
+        <v>2.9213</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2092</v>
+        <v>1.6171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3526</v>
+        <v>1.3043</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5553</v>
+        <v>0.719</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8945</v>
+        <v>-0.5921</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3391</v>
+        <v>1.3111</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7223</v>
+        <v>1.0347</v>
       </c>
       <c r="K5" t="n">
-        <v>1.401</v>
+        <v>-0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3213</v>
+        <v>1.3374</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.167</v>
+        <v>-0.3157</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5065</v>
+        <v>-0.2895</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6604</v>
+        <v>-0.0262</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9737</v>
+        <v>1.3632</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.5053</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5316</v>
+        <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.671</v>
+        <v>0.7771</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.012</v>
+        <v>0.0621</v>
       </c>
       <c r="V5" t="n">
-        <v>3.6632</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6632</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4435</v>
+        <v>1.042</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3868</v>
+        <v>0.1345</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0567</v>
+        <v>0.9075</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3309</v>
+        <v>0.4998</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7039</v>
+        <v>0.1934</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.0348</v>
+        <v>0.3063</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3071</v>
+        <v>0.0405</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5486</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.2415</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.638</v>
+        <v>0.4592</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8447</v>
+        <v>0.1934</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7933</v>
+        <v>0.2658</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3895</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3632</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7526</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1639</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9423</v>
+        <v>-0.1855</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2215</v>
+        <v>0.2536</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5005</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1812</v>
+        <v>0.5122</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1345</v>
+        <v>-1.2434</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0467</v>
+        <v>1.7556</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4998</v>
+        <v>1.1451</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1934</v>
+        <v>-0.2084</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3063</v>
+        <v>1.3535</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0405</v>
+        <v>0.045</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>0.0244</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4592</v>
+        <v>1.1001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1934</v>
+        <v>-0.2289</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2658</v>
+        <v>1.329</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1947</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1947</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2072</v>
+        <v>-0.2434</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1855</v>
+        <v>-0.3147</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3927</v>
+        <v>0.0713</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6721</v>
+        <v>0.2773</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9444</v>
+        <v>0.8884</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6165</v>
+        <v>-0.6111</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1451</v>
+        <v>-2.3309</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2084</v>
+        <v>2.7039</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3535</v>
+        <v>-5.0348</v>
       </c>
       <c r="J8" t="n">
-        <v>0.045</v>
+        <v>0.3071</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>3.5486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0244</v>
+        <v>-3.2415</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1001</v>
+        <v>-2.638</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2289</v>
+        <v>-0.8447</v>
       </c>
       <c r="O8" t="n">
-        <v>1.329</v>
+        <v>-1.7933</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3895</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>-1.3632</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.7526</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0835</v>
+        <v>0.9977</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0157</v>
+        <v>0.4439</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0678</v>
+        <v>0.5537</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8893</v>
+        <v>-0.2958</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6902</v>
+        <v>-1.2915</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.9957</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0902</v>
@@ -1156,13 +1156,13 @@
         <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.578</v>
+        <v>0.0155</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6091</v>
+        <v>-0.2104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0311</v>
+        <v>0.2259</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.584</v>
+        <v>-1.1724</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5292</v>
+        <v>-3.0705</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9452</v>
+        <v>1.898</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3816</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.328</v>
+        <v>0.6732</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9464</v>
+        <v>-1.3874</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2409</v>
+        <v>-1.5301</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9543</v>
+        <v>1.0468</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7134</v>
+        <v>-2.577</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1406</v>
+        <v>0.8159</v>
       </c>
       <c r="N10" t="n">
         <v>-0.3736</v>
       </c>
       <c r="O10" t="n">
-        <v>0.233</v>
+        <v>1.1896</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7526</v>
+        <v>0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.3105</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5579</v>
+        <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5502</v>
+        <v>-0.8477</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3156</v>
+        <v>-0.5667</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8659</v>
+        <v>-0.281</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6384</v>
+        <v>-1.2293</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3695</v>
+        <v>-4.2302</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7311</v>
+        <v>3.0009</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.3816</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6732</v>
+        <v>-1.328</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3874</v>
+        <v>0.9464</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5301</v>
+        <v>-0.2409</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0468</v>
+        <v>-0.9543</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.577</v>
+        <v>0.7134</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8159</v>
+        <v>-0.1406</v>
       </c>
       <c r="N11" t="n">
         <v>-0.3736</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1896</v>
+        <v>0.233</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3895</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9737</v>
+        <v>-3.3105</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3632</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3137</v>
+        <v>0.9049</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8657</v>
+        <v>-0.0166</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.448</v>
+        <v>0.9215</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7221</v>
+        <v>-1.8612</v>
       </c>
       <c r="E12" t="n">
         <v>-2.4266</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7046</v>
+        <v>0.5654</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6693</v>
@@ -1390,13 +1390,13 @@
         <v>1.9474</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0835</v>
+        <v>-0.0556</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0775</v>
       </c>
       <c r="U12" t="n">
-        <v>0.161</v>
+        <v>0.0219</v>
       </c>
       <c r="V12" t="n">
         <v>0.2795</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.0238</v>
+        <v>10.024</v>
       </c>
       <c r="E13" t="n">
         <v>-2.264200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2881</v>
+        <v>12.2882</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0064</v>
@@ -1438,7 +1438,7 @@
         <v>-0.5462999999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.460199999999999</v>
+        <v>-1.4602</v>
       </c>
       <c r="J13" t="n">
         <v>4.354199999999999</v>
@@ -1447,7 +1447,7 @@
         <v>4.1572</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1967000000000005</v>
+        <v>0.196700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-6.3606</v>
@@ -1459,7 +1459,7 @@
         <v>-1.6569</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.5527</v>
@@ -1468,13 +1468,13 @@
         <v>16.5527</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2103</v>
+        <v>2.2105</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6000000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6103</v>
+        <v>1.6104</v>
       </c>
       <c r="V13" t="n">
         <v>9.8202</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0057</v>
+        <v>1.382</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8345</v>
+        <v>-0.5355</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8402</v>
+        <v>1.9175</v>
       </c>
       <c r="G14" t="n">
         <v>1.2747</v>
@@ -1546,13 +1546,13 @@
         <v>1.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7542</v>
+        <v>-0.3779</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8472</v>
+        <v>-0.5482</v>
       </c>
       <c r="U14" t="n">
-        <v>0.093</v>
+        <v>0.1703</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4884</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.741</v>
+        <v>0.6692</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.284</v>
+        <v>-0.3262</v>
       </c>
       <c r="F16" t="n">
-        <v>1.025</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6069</v>
+        <v>3.4217</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6297</v>
+        <v>-0.6137</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2366</v>
+        <v>4.0354</v>
       </c>
       <c r="J16" t="n">
-        <v>1.295</v>
+        <v>3.3307</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4439</v>
+        <v>0.3388</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8511</v>
+        <v>2.9919</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6879999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0736</v>
+        <v>-0.9525</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3856</v>
+        <v>1.0435</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9474</v>
+        <v>-3.8947</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9474</v>
+        <v>2.5316</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8315</v>
+        <v>-0.3609</v>
       </c>
       <c r="T16" t="n">
-        <v>0.42</v>
+        <v>-0.3212</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4115</v>
+        <v>-0.0397</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6974</v>
+        <v>-1.0284</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0516</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6458</v>
+        <v>-1.5874</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6317</v>
+        <v>0.1225</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1811</v>
+        <v>1.4834</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5495</v>
+        <v>-1.3609</v>
       </c>
       <c r="G17" t="n">
         <v>0.3784</v>
@@ -1780,13 +1780,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4017</v>
+        <v>-0.1075</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8962</v>
+        <v>0.1984</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4945</v>
+        <v>-0.306</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7326</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4583</v>
+        <v>0.0362</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4259</v>
+        <v>-0.6827</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8842</v>
+        <v>0.719</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4217</v>
+        <v>0.6069</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6137</v>
+        <v>-0.6297</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0354</v>
+        <v>1.2366</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3307</v>
+        <v>1.295</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3388</v>
+        <v>0.4439</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9919</v>
+        <v>0.8511</v>
       </c>
       <c r="M18" t="n">
-        <v>0.091</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9525</v>
+        <v>-1.0736</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0435</v>
+        <v>0.3856</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3632</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8947</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5316</v>
+        <v>1.9474</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5718</v>
+        <v>0.1267</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4208</v>
+        <v>0.0212</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.151</v>
+        <v>0.1054</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0284</v>
+        <v>-0.6974</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5590000000000001</v>
+        <v>-0.0516</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5874</v>
+        <v>-0.6458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ELOLA AGUIRREZABALA</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8113</v>
+        <v>-0.7499</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1002</v>
+        <v>0.2236</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2889</v>
+        <v>-0.9734</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5024</v>
+        <v>0.1613</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3469</v>
+        <v>1.3301</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1555</v>
+        <v>-1.1687</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1826</v>
+        <v>0.9665</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0205</v>
+        <v>1.0392</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1621</v>
+        <v>-0.0727</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3198</v>
+        <v>-0.8051</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3263</v>
+        <v>0.2909</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0066</v>
+        <v>-1.096</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1947</v>
+        <v>1.1684</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7789</v>
+        <v>1.1684</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1021</v>
+        <v>-0.7365</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3092</v>
+        <v>-0.7429</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4112</v>
+        <v>0.0064</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2211</v>
+        <v>-1.3432</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2211</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>P. ELOLA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1419</v>
+        <v>-0.8229</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.31</v>
+        <v>-1.0005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1681</v>
+        <v>0.1776</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2732</v>
+        <v>0.5024</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4097</v>
+        <v>0.3469</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1365</v>
+        <v>0.1555</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5246</v>
+        <v>0.1826</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1232</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6478</v>
+        <v>0.1621</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7486</v>
+        <v>0.3198</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5329</v>
+        <v>0.3263</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7843</v>
+        <v>-0.0066</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0866</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1883</v>
+        <v>-0.2095</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2749</v>
+        <v>0.2999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3663</v>
+        <v>-1.2211</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3663</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2931</v>
+        <v>-0.9866</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0755</v>
+        <v>-1.2103</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2176</v>
+        <v>0.2238</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1613</v>
+        <v>-1.2732</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3301</v>
+        <v>-1.4097</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1687</v>
+        <v>0.1365</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9665</v>
+        <v>-0.5246</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0392</v>
+        <v>0.1232</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0727</v>
+        <v>-0.6478</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8051</v>
+        <v>-0.7486</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2909</v>
+        <v>-1.5329</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.096</v>
+        <v>0.7843</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1684</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1684</v>
+        <v>1.5579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2797</v>
+        <v>0.0688</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.042</v>
+        <v>0.288</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2378</v>
+        <v>-0.2192</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3432</v>
+        <v>-0.3663</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3432</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3387</v>
+        <v>-1.4753</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2523</v>
+        <v>-0.7507</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0864</v>
+        <v>-0.7247</v>
       </c>
       <c r="G22" t="n">
         <v>0.5044999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>1.9474</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2873</v>
+        <v>0.1507</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5344</v>
+        <v>0.036</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2471</v>
+        <v>0.1147</v>
       </c>
       <c r="V22" t="n">
         <v>-3.1042</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4286</v>
+        <v>-1.8854</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2018</v>
+        <v>-2.9028</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7732</v>
+        <v>1.0174</v>
       </c>
       <c r="G23" t="n">
         <v>0.5345</v>
@@ -2248,13 +2248,13 @@
         <v>1.5579</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1468</v>
+        <v>-0.6036</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7328</v>
+        <v>-0.4338</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.414</v>
+        <v>-0.1698</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4532</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>M. LARRANAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2468</v>
+        <v>-2.8901</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3439</v>
+        <v>-2.9589</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0971</v>
+        <v>0.0687</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5927</v>
+        <v>-2.428</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7416</v>
+        <v>-1.3666</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8511</v>
+        <v>-1.0614</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4704</v>
+        <v>-1.2385</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9114</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.3207</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1223</v>
+        <v>-1.1894</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1698</v>
+        <v>-1.4487</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.292</v>
+        <v>0.2592</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.9474</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3632</v>
+        <v>1.1684</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3154</v>
+        <v>0.3168</v>
       </c>
       <c r="T24" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.227</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2415</v>
+        <v>0.0897</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3853</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. LARRANAGA ORMAZABAL</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.516</v>
+        <v>-3.675</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5569</v>
+        <v>-4.5433</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0409</v>
+        <v>0.8683</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.428</v>
+        <v>-2.5927</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3666</v>
+        <v>-1.7416</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0614</v>
+        <v>-0.8511</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2385</v>
+        <v>-2.4704</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08210000000000001</v>
+        <v>-1.9114</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3207</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1894</v>
+        <v>-0.1223</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4487</v>
+        <v>0.1698</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2592</v>
+        <v>-0.292</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7789</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.9474</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1684</v>
+        <v>1.3632</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3091</v>
+        <v>-0.1128</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.371</v>
+        <v>-0.1255</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0619</v>
+        <v>0.0127</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.3853</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.3853</v>
       </c>
     </row>
     <row r="26">
@@ -2437,40 +2437,40 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.0239</v>
+        <v>-9.359500000000001</v>
       </c>
       <c r="E26" t="n">
         <v>-12.2881</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2641</v>
+        <v>2.9288</v>
       </c>
       <c r="G26" t="n">
-        <v>2.0063</v>
+        <v>2.006300000000001</v>
       </c>
       <c r="H26" t="n">
         <v>0.5462999999999996</v>
       </c>
       <c r="I26" t="n">
-        <v>1.460199999999999</v>
+        <v>1.4602</v>
       </c>
       <c r="J26" t="n">
         <v>6.3607</v>
       </c>
       <c r="K26" t="n">
-        <v>4.703499999999999</v>
+        <v>4.7035</v>
       </c>
       <c r="L26" t="n">
         <v>1.657</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.354000000000001</v>
+        <v>-4.354</v>
       </c>
       <c r="N26" t="n">
         <v>-4.157299999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1967999999999998</v>
+        <v>-0.1968</v>
       </c>
       <c r="P26" t="n">
         <v>1.110223024625157e-16</v>
@@ -2482,13 +2482,13 @@
         <v>16.5527</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.2102</v>
+        <v>-1.5458</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.6102</v>
+        <v>-1.6105</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6002</v>
+        <v>0.0644</v>
       </c>
       <c r="V26" t="n">
         <v>-9.8201</v>
